--- a/data-manipulation-scripts/sheets-cleanup/sheets/PISCAS - 18_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/PISCAS - 18_01.xlsx
@@ -1815,7 +1815,9 @@
       <c r="C76" s="4">
         <v>3.0</v>
       </c>
-      <c r="D76" s="5"/>
+      <c r="D76" s="4">
+        <v>8.0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
